--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.1354166666666667</v>
+        <v>0.1043478260869565</v>
       </c>
       <c r="B2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.352112676056338</v>
+        <v>0.1901408450704225</v>
       </c>
       <c r="D2">
-        <v>0.8679245283018868</v>
+        <v>0.905511811023622</v>
       </c>
       <c r="E2">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,16 +420,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.1043478260869565</v>
+        <v>0.1130434782608696</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.1901408450704225</v>
+        <v>0.1971830985915493</v>
       </c>
       <c r="D2">
-        <v>0.905511811023622</v>
+        <v>0.8976377952755905</v>
       </c>
       <c r="E2">
         <v>115</v>
